--- a/resource/groundTruths/requirement/CF_M09_ground_truth_requirement.xlsx
+++ b/resource/groundTruths/requirement/CF_M09_ground_truth_requirement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/requirement/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76AEBB97-9DDB-494C-821C-FBBAF79D72A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22A99A9-292C-B140-99F4-3F693F854DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="166">
   <si>
     <t>Document ID</t>
   </si>
@@ -449,45 +449,24 @@
     <t>CF_M09_R60</t>
   </si>
   <si>
-    <t>CF_M09_C10</t>
-  </si>
-  <si>
     <t>Decoupling</t>
   </si>
   <si>
-    <t>CF_M09_C11</t>
-  </si>
-  <si>
     <t>Ease</t>
   </si>
   <si>
-    <t>CF_M09_C12</t>
-  </si>
-  <si>
     <t>Scalability</t>
   </si>
   <si>
-    <t>CF_M09_C13</t>
-  </si>
-  <si>
     <t>Performance</t>
   </si>
   <si>
-    <t>CF_M09_C14</t>
-  </si>
-  <si>
     <t>Compatability</t>
   </si>
   <si>
-    <t>CF_M09_C15</t>
-  </si>
-  <si>
     <t>Popularity</t>
   </si>
   <si>
-    <t>CF_M09_C16</t>
-  </si>
-  <si>
     <t>Price</t>
   </si>
   <si>
@@ -516,6 +495,30 @@
   </si>
   <si>
     <t>Privacy</t>
+  </si>
+  <si>
+    <t>*CF_M09_C10</t>
+  </si>
+  <si>
+    <t>*CF_M09_C11</t>
+  </si>
+  <si>
+    <t>*CF_M09_C12</t>
+  </si>
+  <si>
+    <t>*CF_M09_C13</t>
+  </si>
+  <si>
+    <t>*CF_M09_C14</t>
+  </si>
+  <si>
+    <t>*CF_M09_C15</t>
+  </si>
+  <si>
+    <t>*CF_M09_C16</t>
+  </si>
+  <si>
+    <t>Concept</t>
   </si>
 </sst>
 </file>
@@ -910,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>165</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -2329,7 +2332,7 @@
         <v>71</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D2" s="2"/>
     </row>
@@ -2341,7 +2344,7 @@
         <v>72</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -2353,7 +2356,7 @@
         <v>73</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D4" s="2"/>
     </row>
@@ -2365,7 +2368,7 @@
         <v>74</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D5" s="2"/>
     </row>
@@ -2377,7 +2380,7 @@
         <v>75</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D6" s="2"/>
     </row>
@@ -2389,7 +2392,7 @@
         <v>76</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D7" s="2"/>
     </row>
@@ -2401,7 +2404,7 @@
         <v>77</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -2413,7 +2416,7 @@
         <v>78</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D9" s="2"/>
     </row>
@@ -2425,64 +2428,64 @@
         <v>79</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="B15" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="B16" s="4" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B17" s="4" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B18" s="4" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B19" s="4" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B20" s="4" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B21" s="4" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/resource/groundTruths/requirement/CF_M09_ground_truth_requirement.xlsx
+++ b/resource/groundTruths/requirement/CF_M09_ground_truth_requirement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/requirement/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04515A78-36EC-BA4A-A62D-6F6818FAE6C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C158CDAB-E042-4848-874F-E4F63B8B7382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="166">
   <si>
     <t>Document ID</t>
   </si>
@@ -513,6 +513,12 @@
   </si>
   <si>
     <t>Fixed Type</t>
+  </si>
+  <si>
+    <t>*CF_M09_C17</t>
+  </si>
+  <si>
+    <t>Security</t>
   </si>
 </sst>
 </file>
@@ -2213,7 +2219,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2387,6 +2393,14 @@
         <v>145</v>
       </c>
     </row>
+    <row r="22" spans="2:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B22" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
